--- a/static/sample_contacts.xlsx
+++ b/static/sample_contacts.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -427,6 +427,21 @@
           <t>customer_name</t>
         </is>
       </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>enterprise_id</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>agent_id</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>campaign_id</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -439,6 +454,21 @@
           <t>Prem</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>ent_admin_101</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>agent_sales_01</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>cmp_spring_2026</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -449,6 +479,21 @@
       <c r="B3" t="inlineStr">
         <is>
           <t>Test User</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>ent_admin_101</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>agent_sales_01</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>cmp_spring_2026</t>
         </is>
       </c>
     </row>
